--- a/XLibur.Tests/Resource/Examples/Misc/TabColors.xlsx
+++ b/XLibur.Tests/Resource/Examples/Misc/TabColors.xlsx
@@ -365,16 +365,11 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:tabColor rgb="FFFF0000"/>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -382,16 +377,11 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:tabColor theme="6"/>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -399,16 +389,11 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:tabColor indexed="24"/>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -416,15 +401,10 @@
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
   <x:sheetPr>
     <x:tabColor rgb="FF171717"/>
-    <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
   <x:dimension ref="A1"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData/>
-  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
-  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
-  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
-  <x:headerFooter/>
-  <x:tableParts count="0"/>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>